--- a/data/TTC/最新版班表/2026-10/TTC_TM.xlsx
+++ b/data/TTC/最新版班表/2026-10/TTC_TM.xlsx
@@ -1281,20 +1281,14 @@
           <t>林惠苓</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1302,12 +1296,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1392,12 +1383,9 @@
 8:10</t>
         </is>
       </c>
-      <c r="S8" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="T8" s="1" t="inlineStr">
@@ -1421,12 +1409,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="W8" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="X8" s="1" t="inlineStr">
@@ -1616,12 +1601,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="U9" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-WRSL
-17:30
-8:00</t>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>WRSL</t>
         </is>
       </c>
       <c r="V9" s="1" t="inlineStr">
@@ -1764,12 +1746,9 @@
 8:15</t>
         </is>
       </c>
-      <c r="L10" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="M10" s="1" t="inlineStr">
@@ -1832,20 +1811,14 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="V10" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="W10" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -2088,12 +2061,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AB11" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUTS
-17:30
-8:00</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>LUTS</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2513,28 +2483,19 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="AB13" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AC13" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AD13" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
     </row>
@@ -2601,12 +2562,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2859,20 +2817,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="Q15" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="R15" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2888,12 +2840,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="U15" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-WRSL
-17:30
-8:00</t>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>WRSL</t>
         </is>
       </c>
       <c r="V15" s="1" t="inlineStr">
@@ -2976,36 +2925,24 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="G16" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -3018,12 +2955,9 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -3371,12 +3305,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD17" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
     </row>
@@ -3492,12 +3423,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="Q18" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -3550,10 +3478,10 @@
       </c>
       <c r="Y18" s="1" t="inlineStr">
         <is>
-          <t>7:00
+          <t>8:37
 CM1012
-15:00
-8:00</t>
+16:40
+8:03</t>
         </is>
       </c>
       <c r="Z18" s="1" t="inlineStr">
@@ -3568,8 +3496,8 @@
         <is>
           <t>5:15
 CM0001
-13:20
-8:05</t>
+13:15
+8:00</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -3631,20 +3559,14 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="G19" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="H19" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -3766,36 +3688,24 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="Z19" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AA19" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AB19" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AC19" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -3882,12 +3792,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="L20" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="M20" s="1" t="inlineStr">
@@ -4049,12 +3956,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="G21" s="1" t="inlineStr">
@@ -4087,44 +3991,29 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="L21" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="M21" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="N21" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="O21" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -4132,12 +4021,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="Q21" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -4333,12 +4219,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="P22" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -4383,12 +4266,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="W22" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="X22" s="1" t="inlineStr">
@@ -4619,36 +4499,24 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="Z23" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AA23" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AB23" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AC23" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -4724,44 +4592,29 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="L24" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="M24" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="N24" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="O24" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -4769,12 +4622,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="Q24" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -4907,12 +4757,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="H25" s="1" t="inlineStr">
@@ -5046,36 +4893,24 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="Z25" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AA25" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AB25" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AC25" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5340,20 +5175,14 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="H27" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -5361,28 +5190,19 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="J27" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="L27" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -5524,36 +5344,24 @@
           <t>龍穎</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="E28" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -5692,36 +5500,24 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="Z28" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AA28" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AB28" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AC28" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -5906,36 +5702,24 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="Z29" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AA29" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AB29" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AC29" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6048,20 +5832,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="P30" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="Q30" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -6121,28 +5899,19 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="AA30" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AB30" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AC30" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6162,28 +5931,19 @@
           <t>黃偉誌</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6305,12 +6065,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="W31" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -6377,12 +6134,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="D32" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -6395,20 +6149,14 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="G32" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="H32" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -6416,12 +6164,9 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="J32" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="K32" s="1" t="inlineStr">
@@ -6445,12 +6190,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="N32" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -6508,12 +6250,9 @@
 8:06</t>
         </is>
       </c>
-      <c r="W32" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -6531,12 +6270,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="AA32" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AB32" s="1" t="inlineStr">
@@ -6889,20 +6625,14 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="Q34" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="R34" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -6910,20 +6640,14 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="T34" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="U34" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">

--- a/data/TTC/最新版班表/2026-10/TTC_TM.xlsx
+++ b/data/TTC/最新版班表/2026-10/TTC_TM.xlsx
@@ -844,203 +844,181 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>12:40
+          <t>-
 CM1504
-20:40
-8:00</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+-
+-</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>16:20
+          <t>-
 CM0525
-24:31
-8:11</t>
+-
+-</t>
         </is>
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>15:20
+          <t>-
 CM0523
-24:31
-9:11</t>
+-
+-</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>15:40
-CM0522
-24:01
-8:21</t>
-        </is>
-      </c>
-      <c r="H6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+          <t>-
+CM5902
+-
+-</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>13:52
+          <t>-
 DO2W
 CM5901
-22:14
-8:22</t>
+-
+-</t>
         </is>
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>11:47
+          <t>-
 CM0028
-21:40
-9:53</t>
+-
+-</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>11:45
-CM0026
-19:45
-8:00</t>
-        </is>
-      </c>
-      <c r="L6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="M6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+          <t>-
+CM0022
+-
+-</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>7:42
-CM0014
-15:42
-8:00</t>
+          <t>-
+CM1026
+-
+-</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>5:00
-STD1
-13:00
-8:00</t>
+          <t>-
+CM0513
+-
+-</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr">
         <is>
-          <t>5:44
-CM2006
-13:52
-8:08</t>
-        </is>
-      </c>
-      <c r="Q6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+          <t>-
+CM1019
+-
+-</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr">
         <is>
-          <t>5:44
+          <t>-
 CM0006
-13:59
-8:15</t>
+-
+-</t>
         </is>
       </c>
       <c r="S6" s="1" t="inlineStr">
         <is>
-          <t>5:40
-CM0004
-13:56
-8:16</t>
+          <t>-
+CM0512
+-
+-</t>
         </is>
       </c>
       <c r="T6" s="1" t="inlineStr">
         <is>
-          <t>5:35
-CM0002
-14:40
-9:05</t>
-        </is>
-      </c>
-      <c r="U6" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-FAC
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="V6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="W6" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="X6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+          <t>-
+CM0511
+-
+-</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>FAC</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Y6" s="1" t="inlineStr">
         <is>
-          <t>8:37
-CM1012
-16:40
-8:03</t>
+          <t>09:37
+CM5903
+18:08
+08:31</t>
         </is>
       </c>
       <c r="Z6" s="1" t="inlineStr">
         <is>
-          <t>5:50
-CM0007
-13:50
-8:00</t>
+          <t>08:19
+CM5901
+16:19
+08:00</t>
         </is>
       </c>
       <c r="AA6" s="1" t="inlineStr">
         <is>
-          <t>5:15
-CM0001
-13:15
-8:00</t>
-        </is>
-      </c>
-      <c r="AB6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+          <t>06:02
+CM0008
+14:20
+08:18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC6" s="1" t="inlineStr">
@@ -1048,7 +1026,7 @@
           <t>16:13
 CM2523
 24:31
-8:18</t>
+08:18</t>
         </is>
       </c>
       <c r="AD6" s="1" t="inlineStr">
@@ -1056,7 +1034,7 @@
           <t>16:28
 CM0526
 24:31
-8:03</t>
+08:03</t>
         </is>
       </c>
     </row>

--- a/data/TTC/最新版班表/2026-10/TTC_TM.xlsx
+++ b/data/TTC/最新版班表/2026-10/TTC_TM.xlsx
@@ -844,10 +844,10 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:40
 CM1504
--
--</t>
+20:40
+08:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -857,26 +857,26 @@
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:20
 CM0525
--
--</t>
+24:31
+08:11</t>
         </is>
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:20
 CM0523
--
--</t>
+24:31
+09:11</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:17
 CM5902
--
--</t>
+23:42
+08:25</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -886,27 +886,27 @@
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>13:52
 DO2W
 CM5901
--
--</t>
+22:14
+08:22</t>
         </is>
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>11:47
 CM0028
--
--</t>
+21:40
+09:53</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>10:52
 CM0022
--
--</t>
+19:52
+09:00</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -921,26 +921,26 @@
       </c>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>11:45
 CM1026
--
--</t>
+20:14
+08:29</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:25
 CM0513
--
--</t>
+22:14
+09:49</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>10:20
 CM1019
--
--</t>
+18:20
+08:00</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -950,26 +950,26 @@
       </c>
       <c r="R6" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:44
 CM0006
--
--</t>
+13:59
+08:15</t>
         </is>
       </c>
       <c r="S6" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>13:20
 CM0512
--
--</t>
+21:59
+08:39</t>
         </is>
       </c>
       <c r="T6" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>13:56
 CM0511
--
--</t>
+21:56
+08:00</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1051,10 +1051,10 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:15
 CM2001
--
--</t>
+13:56
+08:41</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1069,26 +1069,26 @@
       </c>
       <c r="F7" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:31
 CM0011
--
--</t>
+14:59
+08:28</t>
         </is>
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:02
 CM1008
--
--</t>
+14:40
+08:38</t>
         </is>
       </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:15
 CM1001
--
--</t>
+13:15
+08:00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1103,26 +1103,26 @@
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:31
 CM1011
--
--</t>
+14:59
+08:28</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:15
 CM0001
--
--</t>
+13:15
+08:00</t>
         </is>
       </c>
       <c r="M7" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:41
 CM0011
--
--</t>
+14:59
+08:18</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1132,34 +1132,34 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:17
 CM0518
--
--</t>
+23:42
+08:25</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:40
 CM1504
--
--</t>
+20:40
+08:00</t>
         </is>
       </c>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:08
 CM0514
--
--</t>
+24:08
+08:00</t>
         </is>
       </c>
       <c r="R7" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:13
 CM1501
--
--</t>
+20:14
+08:01</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1286,27 +1286,27 @@
       </c>
       <c r="H8" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>09:20
 CM0018
--
--</t>
+18:45
+09:25</t>
         </is>
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>07:33
 DO2W
 CM0013
--
--</t>
+16:37
+09:04</t>
         </is>
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:02
 CM1009
--
--</t>
+14:31
+08:29</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1316,26 +1316,26 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:00
 STD1
--
--</t>
+13:00
+08:00</t>
         </is>
       </c>
       <c r="M8" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:44
 CM0006
--
--</t>
+13:59
+08:15</t>
         </is>
       </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:40
 CM1004
--
--</t>
+13:56
+08:16</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1355,10 +1355,10 @@
       </c>
       <c r="R8" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:35
 CM1002
--
--</t>
+13:45
+08:10</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1368,10 +1368,10 @@
       </c>
       <c r="T8" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:15
 CM0001
--
--</t>
+13:15
+08:00</t>
         </is>
       </c>
       <c r="U8" s="1" t="inlineStr">
@@ -1462,34 +1462,34 @@
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:44
 CM0006
--
--</t>
+13:59
+08:15</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:50
 CM0007
--
--</t>
+13:50
+08:00</t>
         </is>
       </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:35
 CM0002
--
--</t>
+14:40
+09:05</t>
         </is>
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:40
 CM1004
--
--</t>
+13:56
+08:16</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1505,18 +1505,18 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:35
 CM2003
--
--</t>
+13:40
+08:05</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:15
 CM0001
--
--</t>
+13:15
+08:00</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1531,18 +1531,18 @@
       </c>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>08:30
 DRILL
--
--</t>
+17:30
+08:00</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:40
 CM0504
--
--</t>
+20:40
+08:00</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1552,18 +1552,18 @@
       </c>
       <c r="Q9" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>11:54
 CM0028
--
--</t>
+21:40
+09:46</t>
         </is>
       </c>
       <c r="R9" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>11:45
 CM0026
--
--</t>
+19:45
+08:00</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1573,10 +1573,10 @@
       </c>
       <c r="T9" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>08:30
 OGT2
--
--</t>
+17:30
+08:00</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1662,10 +1662,10 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>10:45
 CM0021
--
--</t>
+18:45
+08:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1680,35 +1680,35 @@
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:44
 CM0006
--
--</t>
+13:59
+08:15</t>
         </is>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:35
 CM0003
--
--</t>
+13:45
+08:10</t>
         </is>
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:02
 CM3008
--
--</t>
+14:02
+08:00</t>
         </is>
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:00
 DO2W
 STD1
--
--</t>
+13:00
+08:00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1718,10 +1718,10 @@
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:44
 CM0006
--
--</t>
+13:59
+08:15</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1731,10 +1731,10 @@
       </c>
       <c r="M10" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>08:13
 CM0015
--
--</t>
+16:13
+08:00</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1749,18 +1749,18 @@
       </c>
       <c r="P10" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>11:45
 CM0027
--
--</t>
+19:45
+08:00</t>
         </is>
       </c>
       <c r="Q10" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>10:40
 CM0020
--
--</t>
+19:14
+08:34</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1770,18 +1770,18 @@
       </c>
       <c r="S10" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:40
 CM0004
--
--</t>
+13:56
+08:16</t>
         </is>
       </c>
       <c r="T10" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:35
 CM0002
--
--</t>
+14:40
+09:05</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1865,18 +1865,18 @@
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:13
 CM1501
--
--</t>
+20:14
+08:01</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:37
 CM0503
--
--</t>
+20:37
+08:00</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1886,35 +1886,35 @@
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:14
 CM0503
--
--</t>
+20:14
+08:00</t>
         </is>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:08
 CM2501
--
--</t>
+20:14
+08:06</t>
         </is>
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:20
 DO2W
 CM0502
--
--</t>
+20:20
+08:00</t>
         </is>
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>10:40
 CM0020
--
--</t>
+19:14
+08:34</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1924,34 +1924,34 @@
       </c>
       <c r="L11" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:40
 CM0522
--
--</t>
+24:01
+08:21</t>
         </is>
       </c>
       <c r="M11" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:30
 STD8
--
--</t>
+24:30
+08:00</t>
         </is>
       </c>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:31
 CM2525
--
--</t>
+24:31
+08:00</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:08
 CM5901
--
--</t>
+24:08
+08:00</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1966,26 +1966,26 @@
       </c>
       <c r="R11" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:02
 CM2008
--
--</t>
+14:02
+08:00</t>
         </is>
       </c>
       <c r="S11" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:35
 CM0002
--
--</t>
+14:40
+09:05</t>
         </is>
       </c>
       <c r="T11" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:37
 CM0503
--
--</t>
+20:37
+08:00</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -2071,10 +2071,10 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>11:13
 CM0025
--
--</t>
+21:04
+09:51</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2089,43 +2089,43 @@
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:40
 CM0522
--
--</t>
+24:01
+08:21</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:20
 CM1523
--
--</t>
+24:31
+09:11</t>
         </is>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>14:50
 CM0518
--
--</t>
+22:50
+08:00</t>
         </is>
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>14:17
 DO2W
 CM5902
--
--</t>
+23:27
+09:10</t>
         </is>
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>14:13
 CM1513
--
--</t>
+22:14
+08:01</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2135,34 +2135,34 @@
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:02
 CM0008
--
--</t>
+14:20
+08:18</t>
         </is>
       </c>
       <c r="M12" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:40
 CM0004
--
--</t>
+13:56
+08:16</t>
         </is>
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:37
 CM0503
--
--</t>
+20:37
+08:00</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>13:08
 CM0509
--
--</t>
+21:14
+08:06</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2172,34 +2172,34 @@
       </c>
       <c r="Q12" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>10:45
 CM0021
--
--</t>
+18:45
+08:00</t>
         </is>
       </c>
       <c r="R12" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>10:52
 CM0022
--
--</t>
+19:52
+09:00</t>
         </is>
       </c>
       <c r="S12" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>08:13
 CM0015
--
--</t>
+16:13
+08:00</t>
         </is>
       </c>
       <c r="T12" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>08:30
 OGT2
--
--</t>
+17:30
+08:00</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2285,26 +2285,26 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:30
 STD8
--
--</t>
+24:30
+08:00</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:52
 CM1525
--
--</t>
+24:31
+08:39</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>13:56
 CM0511
--
--</t>
+21:56
+08:00</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2319,27 +2319,27 @@
       </c>
       <c r="H13" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>13:00
 CM0509
--
--</t>
+21:00
+08:00</t>
         </is>
       </c>
       <c r="I13" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>13:08
 DO2W
 CM0508
--
--</t>
+21:08
+08:00</t>
         </is>
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>13:56
 CM1518
--
--</t>
+23:42
+09:46</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2349,34 +2349,34 @@
       </c>
       <c r="L13" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:14
 CM0501
--
--</t>
+20:14
+08:00</t>
         </is>
       </c>
       <c r="M13" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:14
 CM0501
--
--</t>
+20:14
+08:00</t>
         </is>
       </c>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>10:56
 CM1022
--
--</t>
+19:52
+08:56</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>10:20
 CM0019
--
--</t>
+19:14
+08:54</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2391,26 +2391,26 @@
       </c>
       <c r="R13" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>07:00
 CM1012
--
--</t>
+15:00
+08:00</t>
         </is>
       </c>
       <c r="S13" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:50
 CM0007
--
--</t>
+13:50
+08:00</t>
         </is>
       </c>
       <c r="T13" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>08:30
 OGT2
--
--</t>
+17:30
+08:00</t>
         </is>
       </c>
       <c r="U13" s="1" t="inlineStr">
@@ -2500,34 +2500,34 @@
       </c>
       <c r="E14" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>08:13
 CM0015
--
--</t>
+16:13
+08:00</t>
         </is>
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>08:13
 CM0015
--
--</t>
+16:13
+08:00</t>
         </is>
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:41
 CM0011
--
--</t>
+15:59
+09:18</t>
         </is>
       </c>
       <c r="H14" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:21
 CM5901
--
--</t>
+14:40
+08:19</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2552,42 +2552,42 @@
       </c>
       <c r="M14" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>08:30
 OGT2
--
--</t>
+17:30
+08:00</t>
         </is>
       </c>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:30
 STD8
--
--</t>
+24:30
+08:00</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:13
 CM2523
--
--</t>
+24:31
+08:18</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:37
 CM2522
--
--</t>
+24:01
+08:24</t>
         </is>
       </c>
       <c r="Q14" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>14:13
 CM1513
--
--</t>
+22:14
+08:01</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2602,10 +2602,10 @@
       </c>
       <c r="T14" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:20
 CM0525
--
--</t>
+24:31
+08:11</t>
         </is>
       </c>
       <c r="U14" s="1" t="inlineStr">
@@ -2696,18 +2696,18 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:17
 CM1526
--
--</t>
+24:31
+08:14</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:40
 CM0522
--
--</t>
+24:01
+08:21</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2722,35 +2722,35 @@
       </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>09:57
 CM1022
--
--</t>
+19:14
+09:17</t>
         </is>
       </c>
       <c r="H15" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>10:17
 CM5904
--
--</t>
+18:17
+08:00</t>
         </is>
       </c>
       <c r="I15" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>11:45
 DO2W
 CM0027
--
--</t>
+19:45
+08:00</t>
         </is>
       </c>
       <c r="J15" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>10:14
 CM3501
--
--</t>
+20:04
+09:50</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2765,34 +2765,34 @@
       </c>
       <c r="M15" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:35
 CM0002
--
--</t>
+14:40
+09:05</t>
         </is>
       </c>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:00
 STD1
--
--</t>
+13:00
+08:00</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:44
 CM0006
--
--</t>
+13:59
+08:15</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:15
 CM0001
--
--</t>
+13:15
+08:00</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2812,10 +2812,10 @@
       </c>
       <c r="T15" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>10:00
 MT6
--
--</t>
+18:00
+08:00</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2945,18 +2945,18 @@
       </c>
       <c r="L16" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>13:20
 CM0512
--
--</t>
+21:59
+08:39</t>
         </is>
       </c>
       <c r="M16" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>13:56
 CM0511
--
--</t>
+21:56
+08:00</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2966,18 +2966,18 @@
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:04
 CM0507
--
--</t>
+21:00
+08:56</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:20
 CM0502
--
--</t>
+20:20
+08:00</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2987,26 +2987,26 @@
       </c>
       <c r="R16" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:00
 STD1
--
--</t>
+13:00
+08:00</t>
         </is>
       </c>
       <c r="S16" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:02
 CM0008
--
--</t>
+14:20
+08:18</t>
         </is>
       </c>
       <c r="T16" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:40
 CM0004
--
--</t>
+13:56
+08:16</t>
         </is>
       </c>
       <c r="U16" s="1" t="inlineStr">
@@ -3095,34 +3095,34 @@
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:40
 CM0522
--
--</t>
+24:01
+08:21</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:20
 CM0523
--
--</t>
+24:31
+09:11</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:40
 CM0522
--
--</t>
+24:01
+08:21</t>
         </is>
       </c>
       <c r="F17" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>13:56
 CM0511
--
--</t>
+21:56
+08:00</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -3147,26 +3147,26 @@
       </c>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:52
 CM1525
--
--</t>
+24:31
+08:39</t>
         </is>
       </c>
       <c r="L17" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:20
 CM0523
--
--</t>
+24:31
+09:11</t>
         </is>
       </c>
       <c r="M17" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:40
 CM0522
--
--</t>
+24:01
+08:21</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -3176,34 +3176,34 @@
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:30
 STD8
--
--</t>
+24:30
+08:00</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:08
 CM0527
--
--</t>
+24:08
+08:00</t>
         </is>
       </c>
       <c r="Q17" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:17
 CM1526
--
--</t>
+24:31
+08:14</t>
         </is>
       </c>
       <c r="R17" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:40
 CM0522
--
--</t>
+24:01
+08:21</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -3213,10 +3213,10 @@
       </c>
       <c r="T17" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>08:30
 OGT2
--
--</t>
+17:30
+08:00</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -3307,26 +3307,26 @@
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:40
 CM0004
--
--</t>
+13:56
+08:16</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:02
 CM0008
--
--</t>
+14:20
+08:18</t>
         </is>
       </c>
       <c r="F18" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:15
 CM0001
--
--</t>
+13:15
+08:00</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -3336,35 +3336,35 @@
       </c>
       <c r="H18" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:31
 CM1526
--
--</t>
+24:31
+08:00</t>
         </is>
       </c>
       <c r="I18" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:31
 DO2W
 CM3523
--
--</t>
+24:31
+08:00</t>
         </is>
       </c>
       <c r="J18" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:08
 CM0514
--
--</t>
+24:08
+08:00</t>
         </is>
       </c>
       <c r="K18" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:40
 CM0522
--
--</t>
+24:01
+08:21</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -3374,26 +3374,26 @@
       </c>
       <c r="M18" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:50
 CM0007
--
--</t>
+13:50
+08:00</t>
         </is>
       </c>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:35
 CM0003
--
--</t>
+13:37
+08:02</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:35
 CM1002
--
--</t>
+13:45
+08:10</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -3413,18 +3413,18 @@
       </c>
       <c r="S18" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:41
 CM0011
--
--</t>
+14:59
+08:18</t>
         </is>
       </c>
       <c r="T18" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:00
 STD1
--
--</t>
+13:00
+08:00</t>
         </is>
       </c>
       <c r="U18" s="1" t="inlineStr">
@@ -3510,26 +3510,26 @@
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>10:40
 CM0020
--
--</t>
+19:14
+08:34</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>10:52
 CM0022
--
--</t>
+19:52
+09:00</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:30
 STD8
--
--</t>
+24:30
+08:00</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3559,18 +3559,18 @@
       </c>
       <c r="K19" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>09:05
 CM5901
--
--</t>
+17:05
+08:00</t>
         </is>
       </c>
       <c r="L19" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>08:13
 CM0015
--
--</t>
+16:13
+08:00</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -3580,34 +3580,34 @@
       </c>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>08:30
 OGT2
--
--</t>
+17:30
+08:00</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>09:20
 CM0018
--
--</t>
+18:45
+09:25</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>09:17
 CM0017
--
--</t>
+17:17
+08:00</t>
         </is>
       </c>
       <c r="Q19" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>07:42
 CM1014
--
--</t>
+15:42
+08:00</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -3617,18 +3617,18 @@
       </c>
       <c r="S19" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:20
 CM0525
--
--</t>
+24:31
+08:11</t>
         </is>
       </c>
       <c r="T19" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:40
 CM0522
--
--</t>
+24:01
+08:21</t>
         </is>
       </c>
       <c r="U19" s="1" t="inlineStr">
@@ -3710,34 +3710,34 @@
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:37
 CM1503
--
--</t>
+20:37
+08:00</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:14
 CM0501
--
--</t>
+20:14
+08:00</t>
         </is>
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:37
 CM0503
--
--</t>
+20:37
+08:00</t>
         </is>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>11:04
 CM0023
--
--</t>
+21:00
+09:56</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3747,27 +3747,27 @@
       </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>10:20
 DO2W
 CM1019
--
--</t>
+18:52
+08:32</t>
         </is>
       </c>
       <c r="J20" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>08:14
 CM5901
--
--</t>
+17:04
+08:50</t>
         </is>
       </c>
       <c r="K20" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>07:00
 CM1012
--
--</t>
+15:00
+08:00</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -3777,10 +3777,10 @@
       </c>
       <c r="M20" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>08:30
 OGT2
--
--</t>
+17:30
+08:00</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3795,26 +3795,26 @@
       </c>
       <c r="P20" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>07:33
 CM0013
--
--</t>
+16:37
+09:04</t>
         </is>
       </c>
       <c r="Q20" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:00
 STD1
--
--</t>
+13:00
+08:00</t>
         </is>
       </c>
       <c r="R20" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:15
 CM0001
--
--</t>
+13:15
+08:00</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -3920,18 +3920,18 @@
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:31
 CM1011
--
--</t>
+14:59
+08:28</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:15
 CM0001
--
--</t>
+13:15
+08:00</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3941,27 +3941,27 @@
       </c>
       <c r="G21" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:00
 STD1
--
--</t>
+13:00
+08:00</t>
         </is>
       </c>
       <c r="H21" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:44
 CM0006
--
--</t>
+13:59
+08:15</t>
         </is>
       </c>
       <c r="I21" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:15
 DO2W
 CM0001
--
--</t>
+13:15
+08:00</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4011,18 +4011,18 @@
       </c>
       <c r="S21" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>13:56
 CM0511
--
--</t>
+21:56
+08:00</t>
         </is>
       </c>
       <c r="T21" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>13:20
 CM0512
--
--</t>
+21:59
+08:39</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -4110,10 +4110,10 @@
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>13:56
 CM1518
--
--</t>
+23:42
+09:46</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4128,26 +4128,26 @@
       </c>
       <c r="F22" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>13:20
 CM0512
--
--</t>
+21:59
+08:39</t>
         </is>
       </c>
       <c r="G22" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>13:52
 CM0510
--
--</t>
+21:52
+08:00</t>
         </is>
       </c>
       <c r="H22" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>10:20
 CM0019
--
--</t>
+19:14
+08:54</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -4162,34 +4162,34 @@
       </c>
       <c r="K22" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:14
 CM1501
--
--</t>
+20:14
+08:00</t>
         </is>
       </c>
       <c r="L22" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:37
 CM0503
--
--</t>
+20:37
+08:00</t>
         </is>
       </c>
       <c r="M22" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:37
 CM0503
--
--</t>
+20:37
+08:00</t>
         </is>
       </c>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>11:13
 CM0023
--
--</t>
+19:28
+08:15</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -4209,26 +4209,26 @@
       </c>
       <c r="R22" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:40
 CM0004
--
--</t>
+13:56
+08:16</t>
         </is>
       </c>
       <c r="S22" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:00
 STD1
--
--</t>
+13:00
+08:00</t>
         </is>
       </c>
       <c r="T22" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:44
 CM0006
--
--</t>
+13:59
+08:15</t>
         </is>
       </c>
       <c r="U22" s="1" t="inlineStr">
@@ -4314,26 +4314,26 @@
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>11:54
 CM0028
--
--</t>
+21:40
+09:46</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>11:45
 CM0026
--
--</t>
+19:45
+08:00</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>10:52
 CM0022
--
--</t>
+19:52
+09:00</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4348,27 +4348,27 @@
       </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>08:33
 CM5903
--
--</t>
+17:14
+08:41</t>
         </is>
       </c>
       <c r="I23" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>07:14
 DO2W
 CM2011
--
--</t>
+15:14
+08:00</t>
         </is>
       </c>
       <c r="J23" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:15
 CM2001
--
--</t>
+13:56
+08:41</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -4378,34 +4378,34 @@
       </c>
       <c r="L23" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:41
 CM0011
--
--</t>
+14:59
+08:18</t>
         </is>
       </c>
       <c r="M23" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:00
 STD1
--
--</t>
+13:00
+08:00</t>
         </is>
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:44
 CM1006
--
--</t>
+14:20
+08:36</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:40
 CM2004
--
--</t>
+13:40
+08:00</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -4415,26 +4415,26 @@
       </c>
       <c r="Q23" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:40
 CM1504
--
--</t>
+20:40
+08:00</t>
         </is>
       </c>
       <c r="R23" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:37
 CM1503
--
--</t>
+20:37
+08:00</t>
         </is>
       </c>
       <c r="S23" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:14
 CM0501
--
--</t>
+20:14
+08:00</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -4526,43 +4526,43 @@
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:41
 CM0011
--
--</t>
+14:59
+08:18</t>
         </is>
       </c>
       <c r="F24" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:02
 CM0008
--
--</t>
+14:20
+08:18</t>
         </is>
       </c>
       <c r="G24" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:45
 CM0014
--
--</t>
+15:45
+09:00</t>
         </is>
       </c>
       <c r="H24" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:35
 CM1002
--
--</t>
+14:08
+08:33</t>
         </is>
       </c>
       <c r="I24" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:35
 DO2W
 CM1003
--
--</t>
+13:37
+08:02</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -4612,18 +4612,18 @@
       </c>
       <c r="S24" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:20
 CM0523
--
--</t>
+24:31
+09:11</t>
         </is>
       </c>
       <c r="T24" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:30
 STD8
--
--</t>
+24:30
+08:00</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -4711,18 +4711,18 @@
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:14
 CM0524
--
--</t>
+24:31
+09:17</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:30
 STD8
--
--</t>
+24:30
+08:00</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4742,19 +4742,19 @@
       </c>
       <c r="H25" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>08:14
 CM5902
--
--</t>
+16:14
+08:00</t>
         </is>
       </c>
       <c r="I25" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:02
 DO2W
 CM0009
--
--</t>
+14:02
+08:00</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -4764,34 +4764,34 @@
       </c>
       <c r="K25" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:35
 CM1002
--
--</t>
+13:45
+08:10</t>
         </is>
       </c>
       <c r="L25" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:40
 CM0004
--
--</t>
+13:56
+08:16</t>
         </is>
       </c>
       <c r="M25" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:15
 CM0001
--
--</t>
+13:15
+08:00</t>
         </is>
       </c>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>08:30
 OGT2
--
--</t>
+17:30
+08:00</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -4801,18 +4801,18 @@
       </c>
       <c r="P25" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:02
 CM0009
--
--</t>
+14:02
+08:00</t>
         </is>
       </c>
       <c r="Q25" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:35
 CM2003
--
--</t>
+13:40
+08:05</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -4822,18 +4822,18 @@
       </c>
       <c r="S25" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:15
 CM0001
--
--</t>
+13:15
+08:00</t>
         </is>
       </c>
       <c r="T25" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:50
 CM0007
--
--</t>
+13:50
+08:00</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -4910,34 +4910,34 @@
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>07:42
 CM1014
--
--</t>
+15:42
+08:00</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:00
 STD1
--
--</t>
+13:00
+08:00</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:44
 CM0006
--
--</t>
+13:59
+08:15</t>
         </is>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:00
 STD1
--
--</t>
+13:00
+08:00</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4947,35 +4947,35 @@
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:08
 CM2523
--
--</t>
+24:31
+08:23</t>
         </is>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:17
 DO2W
 CM5903
--
--</t>
+24:28
+09:11</t>
         </is>
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:17
 CM0524
--
--</t>
+24:31
+09:14</t>
         </is>
       </c>
       <c r="K26" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:37
 CM1503
--
--</t>
+20:37
+08:00</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -4990,34 +4990,34 @@
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>07:42
 CM0014
--
--</t>
+15:42
+08:00</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:41
 CM0011
--
--</t>
+14:59
+08:18</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:44
 CM2006
--
--</t>
+13:52
+08:08</t>
         </is>
       </c>
       <c r="Q26" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>11:13
 CM0025
--
--</t>
+21:04
+09:51</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -5027,18 +5027,18 @@
       </c>
       <c r="S26" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>10:52
 CM0022
--
--</t>
+19:52
+09:00</t>
         </is>
       </c>
       <c r="T26" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>10:52
 CM0022
--
--</t>
+19:52
+09:00</t>
         </is>
       </c>
       <c r="U26" s="1" t="inlineStr">
@@ -5126,26 +5126,26 @@
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:35
 CM2003
--
--</t>
+13:40
+08:05</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:15
 CM0001
--
--</t>
+13:15
+08:00</t>
         </is>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:00
 STD1
--
--</t>
+13:00
+08:00</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5195,42 +5195,42 @@
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:14
 CM1526
--
--</t>
+24:31
+08:17</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:31
 CM3523
--
--</t>
+24:31
+08:00</t>
         </is>
       </c>
       <c r="Q27" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:40
 CM0522
--
--</t>
+24:01
+08:21</t>
         </is>
       </c>
       <c r="R27" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:52
 CM1525
--
--</t>
+24:31
+08:39</t>
         </is>
       </c>
       <c r="S27" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:30
 STD8
--
--</t>
+24:30
+08:00</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
@@ -5349,35 +5349,35 @@
       </c>
       <c r="H28" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:30
 STD8
--
--</t>
+24:30
+08:00</t>
         </is>
       </c>
       <c r="I28" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:08
 DO2W
 CM0527
--
--</t>
+24:08
+08:00</t>
         </is>
       </c>
       <c r="J28" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:40
 CM0522
--
--</t>
+24:01
+08:21</t>
         </is>
       </c>
       <c r="K28" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:30
 STD8
--
--</t>
+24:30
+08:00</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -5392,34 +5392,34 @@
       </c>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:31
 CM0011
--
--</t>
+14:59
+08:28</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:02
 CM3008
--
--</t>
+14:02
+08:00</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:35
 CM1003
--
--</t>
+13:37
+08:02</t>
         </is>
       </c>
       <c r="Q28" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:15
 CM2001
--
--</t>
+13:56
+08:41</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -5434,10 +5434,10 @@
       </c>
       <c r="T28" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>08:30
 OGT2
--
--</t>
+17:30
+08:00</t>
         </is>
       </c>
       <c r="U28" s="1" t="inlineStr">
@@ -5522,34 +5522,34 @@
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:02
 CM2008
--
--</t>
+14:02
+08:00</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:35
 CM0002
--
--</t>
+14:40
+09:05</t>
         </is>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:40
 CM0004
--
--</t>
+13:56
+08:16</t>
         </is>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:15
 CM0001
--
--</t>
+13:20
+08:05</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -5559,19 +5559,19 @@
       </c>
       <c r="I29" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:37
 DO2W
 CM2522
--
--</t>
+24:01
+08:24</t>
         </is>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:27
 CM5902
--
--</t>
+23:27
+08:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -5586,42 +5586,42 @@
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:20
 CM0525
--
--</t>
+24:31
+08:11</t>
         </is>
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:20
 CM1523
--
--</t>
+24:31
+09:11</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:01
 CM1522
--
--</t>
+24:01
+08:00</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>13:08
 CM0508
--
--</t>
+21:08
+08:00</t>
         </is>
       </c>
       <c r="Q29" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>13:56
 CM1518
--
--</t>
+23:42
+09:46</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -5631,18 +5631,18 @@
       </c>
       <c r="S29" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:37
 CM0503
--
--</t>
+20:37
+08:00</t>
         </is>
       </c>
       <c r="T29" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:14
 CM0501
--
--</t>
+20:14
+08:00</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -5724,34 +5724,34 @@
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:35
 CM1002
--
--</t>
+13:45
+08:10</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:40
 CM0004
--
--</t>
+13:56
+08:16</t>
         </is>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:50
 CM0007
--
--</t>
+13:50
+08:00</t>
         </is>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:44
 CM1006
--
--</t>
+14:59
+09:15</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -5761,27 +5761,27 @@
       </c>
       <c r="I30" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:59
 DO2W
 CM0506
--
--</t>
+20:59
+08:00</t>
         </is>
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:40
 CM1504
--
--</t>
+20:40
+08:00</t>
         </is>
       </c>
       <c r="K30" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>11:45
 CM0026
--
--</t>
+19:45
+08:00</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -5796,18 +5796,18 @@
       </c>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>08:30
 OGT2
--
--</t>
+17:30
+08:00</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:00
 STD1
--
--</t>
+13:00
+08:00</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -5832,10 +5832,10 @@
       </c>
       <c r="T30" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:02
 CM0008
--
--</t>
+14:20
+08:18</t>
         </is>
       </c>
       <c r="U30" s="1" t="inlineStr">
@@ -5936,19 +5936,19 @@
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:31
 CM0011
--
--</t>
+14:59
+08:28</t>
         </is>
       </c>
       <c r="I31" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:44
 DO2W
 CM2006
--
--</t>
+13:52
+08:08</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -5958,76 +5958,29 @@
       </c>
       <c r="K31" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:00
 STD1
--
--</t>
+13:00
+08:00</t>
         </is>
       </c>
       <c r="L31" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:50
 CM0007
--
--</t>
+13:50
+08:00</t>
         </is>
       </c>
       <c r="M31" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:02
 CM0008
--
--</t>
+14:20
+08:18</t>
         </is>
       </c>
       <c r="N31" s="1" t="inlineStr">
-        <is>
-          <t>-
-CM1008
--
--</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="P31" s="1" t="inlineStr">
-        <is>
-          <t>-
-CM0506
--
--</t>
-        </is>
-      </c>
-      <c r="Q31" s="1" t="inlineStr">
-        <is>
-          <t>-
-CM3501
--
--</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="T31" s="1" t="inlineStr">
-        <is>
-          <t>-
-CM0011
--
--</t>
-        </is>
-      </c>
-      <c r="U31" s="1" t="inlineStr">
         <is>
           <t>06:02
 CM1008
@@ -6035,6 +5988,53 @@
 08:38</t>
         </is>
       </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="P31" s="1" t="inlineStr">
+        <is>
+          <t>12:59
+CM0506
+20:59
+08:00</t>
+        </is>
+      </c>
+      <c r="Q31" s="1" t="inlineStr">
+        <is>
+          <t>12:14
+CM3501
+20:14
+08:00</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="T31" s="1" t="inlineStr">
+        <is>
+          <t>06:41
+CM0011
+14:59
+08:18</t>
+        </is>
+      </c>
+      <c r="U31" s="1" t="inlineStr">
+        <is>
+          <t>06:02
+CM1008
+14:40
+08:38</t>
+        </is>
+      </c>
       <c r="V31" s="1" t="inlineStr">
         <is>
           <t>05:15
@@ -6106,10 +6106,10 @@
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:14
 CM3501
--
--</t>
+20:14
+08:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6149,18 +6149,18 @@
       </c>
       <c r="K32" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:02
 CM2008
--
--</t>
+14:02
+08:00</t>
         </is>
       </c>
       <c r="L32" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:35
 CM0002
--
--</t>
+14:40
+09:05</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -6180,18 +6180,18 @@
       </c>
       <c r="P32" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:41
 CM2011
--
--</t>
+14:41
+08:00</t>
         </is>
       </c>
       <c r="Q32" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:02
 CM1009
--
--</t>
+14:31
+08:29</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -6206,10 +6206,10 @@
       </c>
       <c r="T32" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>08:30
 OGT2
--
--</t>
+17:30
+08:00</t>
         </is>
       </c>
       <c r="U32" s="1" t="inlineStr">
@@ -6291,10 +6291,10 @@
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:08
 CM0514
--
--</t>
+24:08
+08:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6304,26 +6304,26 @@
       </c>
       <c r="E33" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:20
 CM0523
--
--</t>
+24:31
+09:11</t>
         </is>
       </c>
       <c r="F33" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:20
 CM0525
--
--</t>
+24:31
+08:11</t>
         </is>
       </c>
       <c r="G33" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:40
 CM0522
--
--</t>
+24:01
+08:21</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -6333,18 +6333,18 @@
       </c>
       <c r="I33" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:17
 CM0526
--
--</t>
+24:31
+08:14</t>
         </is>
       </c>
       <c r="J33" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>13:17
 CM0517
--
--</t>
+23:03
+09:46</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -6354,34 +6354,34 @@
       </c>
       <c r="L33" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:20
 CM0525
--
--</t>
+24:31
+08:11</t>
         </is>
       </c>
       <c r="M33" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:20
 CM0523
--
--</t>
+24:31
+09:11</t>
         </is>
       </c>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:40
 CM0522
--
--</t>
+24:01
+08:21</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:08
 CM2501
--
--</t>
+20:14
+08:06</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -6391,26 +6391,26 @@
       </c>
       <c r="Q33" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:14
 CM0524
--
--</t>
+24:31
+09:17</t>
         </is>
       </c>
       <c r="R33" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:30
 STD8
--
--</t>
+24:30
+08:00</t>
         </is>
       </c>
       <c r="S33" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:40
 CM0522
--
--</t>
+24:01
+08:21</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
@@ -6504,10 +6504,10 @@
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>14:13
 CM1513
--
--</t>
+22:14
+08:01</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -6517,26 +6517,26 @@
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>13:20
 CM0512
--
--</t>
+21:59
+08:39</t>
         </is>
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:14
 CM0501
--
--</t>
+20:14
+08:00</t>
         </is>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:25
 CM5901
--
--</t>
+22:14
+09:49</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -6546,51 +6546,51 @@
       </c>
       <c r="I34" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:30
 DO2W
 STD8
--
--</t>
+24:30
+08:00</t>
         </is>
       </c>
       <c r="J34" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:17
 CM1526
--
--</t>
+24:31
+08:14</t>
         </is>
       </c>
       <c r="K34" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:20
 CM0523
--
--</t>
+24:31
+09:11</t>
         </is>
       </c>
       <c r="L34" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>13:56
 CM0511
--
--</t>
+21:56
+08:00</t>
         </is>
       </c>
       <c r="M34" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>13:20
 CM0512
--
--</t>
+21:59
+08:39</t>
         </is>
       </c>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>13:20
 CM0510
--
--</t>
+21:20
+08:00</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -6702,10 +6702,10 @@
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>13:14
 CM0517
--
--</t>
+23:03
+09:49</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -6720,43 +6720,43 @@
       </c>
       <c r="F35" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>10:52
 CM0022
--
--</t>
+19:52
+09:00</t>
         </is>
       </c>
       <c r="G35" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>11:20
 CM1026
--
--</t>
+21:14
+09:54</t>
         </is>
       </c>
       <c r="H35" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>11:25
 CM0504
--
--</t>
+20:40
+09:15</t>
         </is>
       </c>
       <c r="I35" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>12:40
 DO2W
 CM1504
--
--</t>
+20:40
+08:00</t>
         </is>
       </c>
       <c r="J35" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>11:13
 CM0025
--
--</t>
+21:04
+09:51</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -6766,26 +6766,26 @@
       </c>
       <c r="L35" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>10:52
 CM0022
--
--</t>
+19:52
+09:00</t>
         </is>
       </c>
       <c r="M35" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>10:52
 CM0022
--
--</t>
+19:52
+09:00</t>
         </is>
       </c>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>08:30
 OGT2
--
--</t>
+17:30
+08:00</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -6795,26 +6795,26 @@
       </c>
       <c r="P35" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:28
 CM0526
--
--</t>
+24:31
+08:03</t>
         </is>
       </c>
       <c r="Q35" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>13:14
 CM0517
--
--</t>
+23:03
+09:49</t>
         </is>
       </c>
       <c r="R35" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:20
 CM0523
--
--</t>
+24:31
+09:11</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -6824,10 +6824,10 @@
       </c>
       <c r="T35" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>15:20
 CM0523
--
--</t>
+24:31
+09:11</t>
         </is>
       </c>
       <c r="U35" s="1" t="inlineStr">
@@ -6918,18 +6918,18 @@
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:02
 CM1009
--
--</t>
+14:31
+08:29</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>07:00
 CM1012
--
--</t>
+15:00
+08:00</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -6939,26 +6939,26 @@
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:30
 STD8
--
--</t>
+24:30
+08:00</t>
         </is>
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:17
 CM2525
--
--</t>
+24:31
+08:14</t>
         </is>
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>16:01
 CM1522
--
--</t>
+24:01
+08:00</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -6968,26 +6968,26 @@
       </c>
       <c r="J36" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>07:42
 CM1014
--
--</t>
+15:42
+08:00</t>
         </is>
       </c>
       <c r="K36" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:40
 CM0004
--
--</t>
+13:56
+08:16</t>
         </is>
       </c>
       <c r="L36" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:44
 CM0006
--
--</t>
+13:59
+08:15</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -6997,18 +6997,18 @@
       </c>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:15
 CM0001
--
--</t>
+13:15
+08:00</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:15
 CM1001
--
--</t>
+13:15
+08:00</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -7023,26 +7023,26 @@
       </c>
       <c r="R36" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>06:31
 CM1011
--
--</t>
+14:59
+08:28</t>
         </is>
       </c>
       <c r="S36" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>05:44
 CM0006
--
--</t>
+13:59
+08:15</t>
         </is>
       </c>
       <c r="T36" s="1" t="inlineStr">
         <is>
-          <t>-
+          <t>08:13
 CM0015
--
--</t>
+16:13
+08:00</t>
         </is>
       </c>
       <c r="U36" s="1" t="inlineStr">
